--- a/assets/docs/lop4/Tieng Anh - Lop 4.xlsx
+++ b/assets/docs/lop4/Tieng Anh - Lop 4.xlsx
@@ -871,7 +871,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Digital competence 2.1 CB2a: Pupils look at digital flashcards on the screen, then ask and answer in pairs about their friends’ countries and nationalities.
+          <t>Digital Competency (3.1CB2a): Create simple digital content: Pupils learn to create simple digital pupil cards (including text and images like flags) using basic tools (e.g., Paint, tablet drawing apps) for learning and presentation purposes.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -942,8 +942,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In Unit 2 Time and daily routines, the teacher shows a set of pictures of daily activities with clock faces and plays the model audio
-Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise to listen and choose the right picture and drag the clock hands to the time heard; the computer marks it instantly, so pupils notice when they still confuse times with past and times with to
+          <t>Digital Competence 2.2CB2a: Recognize where data is organized/stored (e.g., recognizing that time and daily routine information is structured and displayed on clocks, timetables, or digital schedules).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -1084,8 +1083,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 2 Time and daily routines, the teacher shows a digital clock face with pictures of daily activities and plays the model audio files of asking and telling the time
-Digital competence Domain 2 (Basic, level 2): The teacher shows the class's blank daily timetable on the screen; each pair of pupils asks and answers about the time they get up, go to school and have dinner, then reads it out for the teacher to fill in the table
+          <t>Digital Competence 3.1CB2b: Choose ways to express oneself through creating a personalized timetable. Pupils select specific daily activities and visual styles to reflect their own identity and routine.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -1156,8 +1154,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the pronunciation part of Unit 3 My week, the teacher plays the audio file of words and sentences with the sound u, first slowly and then at normal speed; pupils listen
-Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the words with the new sound, and match sentences with pictures; the computer marks it instantly, so pupils notice which words they still confuse
+          <t>Digital Competency (3.2CB2a): Select ways to modify and refine information (weekly schedule): Pupils learn how to identify, select, and update correct information in a digital weekly schedule context when presented with incomplete or incorrect data.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -1298,8 +1295,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 3 My week, the teacher shows a set of cards for the days of the week with audio files; pupils listen, then put the days in the right order on the screen
-Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the picture, and fill in the missing days in sentences; the computer marks it instantly, so pupils notice when they still confuse two days that sound alike
+          <t>Digital Competency (2.4CB2a): Select simple digital tools for group collaboration: Pupils work in groups to choose a digital template/table to organize and present their group’s weekly or weekend activities.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -1440,8 +1436,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In Unit 4 My birthday party, the teacher shows a set of pictures of things and activities at a party with an audio recording; pupils listen and match the words with the pictures
-Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the right picture, and fill in the missing words in invitations; the computer marks it instantly, so pupils notice when they still confuse two similar words
+          <t>Digital Competency (1.2CB2a): Detect the accuracy of dates in a listening task: Pupils can identify whether the date mentioned in a digital audio clip/invitation matches the visual information provided on the screen, fostering critical thinking in digital environments.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -1547,7 +1542,7 @@
       <c r="H32" s="4" t="inlineStr">
         <is>
           <t>Digital competence Domain 1 (Basic, level 2): To start Unit 5 Things we can do, the teacher shows a set of activity pictures with model audio; pupils listen and match the activities with the pictures
-Digital competence Domain 2 (Basic, level 2): The teacher shows a three-column table of friends' names, what they can do and what they want to learn; each pair asks and answers in English and then reads out the answers for the teacher to fill in
+Digital competence Domain 2 (Basic, level 2): Pairs ask and answer, T fills a table (name / can do / wants to learn); Ss introduce friends from it
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -1582,8 +1577,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the skills part of Unit 5 Things we can do, the teacher opens the song and learning materials of the lesson in the education sector's digital learning resource library and shows pupils the way…
-Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the picture, and fill in the missing words in sentences; the computer marks it instantly, so pupils notice where they went wrong and listen to that part again
+          <t>Digital Competency (2.6CB2a): Identify digital identity (abilities/hobbies): Pupils recognize that sharing and selecting their abilities (e.g., picking an avatar or a skill badge on hoclieu.vn) is a way to represent themselves (their identity) in a digital environment.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -1724,8 +1718,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 5 Things we can do, the teacher shows a set of activity pictures with model audio; pupils listen and match the activities with the pictures
-Digital competence Domain 2 (Basic, level 2): The teacher shows a three-column table of friends' names, what they can do and what they want to learn; each pair asks and answers in English and then reads out the answers for the teacher to fill in
+          <t>Digital Competency (2.2CB2a): Identify basic citation methods (Imitating digital models): Pupils recognize digital audio/video from Hoclieu.vn as the standard "source" and demonstrate the ability to "cite" it by imitating the exact pronunciation, rhythm, and melody.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -2111,8 +2104,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 2 (Basic, level 2): In the practice part of Unit 7, the teacher plays the lesson's song on the screen for the whole class to sing along, then records the questions and answers about the timetable of a few…
-Digital competence Domain 3 (Basic, level 2): Each group makes a picture timetable: choose subject icons, write the days and two sentences in English introducing their favourite day
+          <t>Digital Competence: CB2a Interaction through various digital technologies. (Students observe and interact with review content on the projection screen)
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -2253,8 +2245,7 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 2 (Basic, level 2): In the practice part of Unit 7, the teacher plays the lesson's song on the screen for the whole class to sing along, then records the questions and answers about the timetable of a few…
-Digital competence Domain 3 (Basic, level 2): Each group makes a picture timetable: choose subject icons, write the days and two sentences in English introducing their favourite day
+          <t>Digital Competence: CB2a Select simple digital technologies to interact. (Students interact with chants through video/audio on projector/speaker)
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -2465,8 +2456,7 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 8 My favourite subjects, the teacher shows a set of pictures of school subjects with model audio files; pupils listen, then match the subject names with the pictures
-Digital competence Domain 2 (Basic, level 2): The teacher shows the class survey table of favourite subjects; each pair asks and answers in English and then reads out the answers for the teacher to tick
+          <t>Digital Competence: CB2a Select simple digital technologies for interaction. (Students interact with the warm-up chant/video on the screen)
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -2677,8 +2667,7 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 9 “Our sports day”, the teacher shows the pictures on the screen and plays the audio, pausing after each part so pupils tick
-Digital competence Domain 2 (Basic, level 2): In the Let's chant activity, the teacher plays the chant with words moving in rhythm on the screen so the whole class chants together in the right rhythm
+          <t>Digital Competence (3.1CB2a): Create simple digital content (e.g., design a Sports Day poster using simple software like MS Paint or PowerPoint).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -2749,8 +2738,7 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 10 “Our summer holidays”, the teacher plays the model audio of the sound ere in the word were
-Digital competence Domain 5 (Basic, level 2): In the Warm-up game Board race, the teacher shows the topic on the screen, and two teams take turns writing words they have learnt
+          <t>Digital Competence (2.2CB2a): Share personal information (e.g., sharing where they went during the holidays) with others through simple digital technologies (simulating sending a message or sharing a photo).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -2891,8 +2879,7 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 10 “Our summer holidays”, the teacher shows pictures of summer holidays on the screen and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the Point and say activity, the teacher shows a shared table “Places visited – Things done”; pairs ask and answer, then come up to write their partner's answers in the table
+          <t>Digital Competence (Integrated): CB2a: Select simple digital tools and technologies for collaborative processes (specifically: choosing a tool to collaborate on telling summer holiday stories).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -3127,8 +3114,7 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 11 “My home”, the teacher plays the model audio of the letter sounds in the lesson
-Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song My house with scrolling lyrics on the screen for the whole class to sing; then divides the class into two groups to sing in turn following the highlighted lyrics and listen…
+          <t>Digital Competence (2.1CB2a): Select simple digital technologies to interact: Choose appropriate simple digital forms (e.g., text message or voice message) to describe their home address to friends.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -3199,8 +3185,7 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 11 “My home”, the teacher shows pictures of things in the house with the words and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the Warm-up game Whispering, after each round of passing the message the teacher shows the original sentence on the screen; the two teams compare what they said with the original
+          <t>Digital Competence (1.2CB2a): Detect the accuracy of the location information heard (from the digital audio recording) by comparing it with visual data (pictures).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -3271,8 +3256,7 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 11 “My home”, the teacher plays the model audio of the letter sounds in the lesson
-Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song My house with scrolling lyrics on the screen for the whole class to sing; then divides the class into two groups to sing in turn following the highlighted lyrics and listen…
+          <t>Digital Competence (3.1CB2a): Create simple digital content (Draw/Describe the house using simple drawing software like Paint or typing text).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -3343,8 +3327,7 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 12 “Jobs”, the teacher shows pictures of people at work with the job names on the screen and plays the model audio
-Digital competence Domain 5 (Basic, level 2): In the Warm-up game Guess the job, the teacher shows photos of objects linked to jobs one by one, such as a stethoscope, a builder's ruler, a chalkboard
+          <t>Digital Competence (2.2CB2a): Recognize where to organize data: Identify the correct folder, file, or digital section to store and share information about "Dream Jobs" on the computer.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -3415,8 +3398,7 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 12 “Jobs”, the teacher plays the model audio of the job words, first slowly and then at normal speed, and shows the words with marks…
-Digital competence Domain 5 (Basic, level 2): In the Warm-up game Lip-reading, the teacher shows a job word to one pupil only, who mouths it silently for the group to guess
+          <t>Digital Competence (NLS): - 1.2CB2a: Evaluate the accuracy of career information (Specifically: Check if the information regarding jobs and workplaces matches the provided visual or audio data).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -3487,8 +3469,7 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 12 “Jobs”, the teacher shows pictures of people at work with the job names on the screen and plays the model audio
-Digital competence Domain 5 (Basic, level 2): In the Warm-up game Guess the job, the teacher shows photos of objects linked to jobs one by one, such as a stethoscope, a builder's ruler, a chalkboard
+          <t>Digital Competence (NLS): - 3.1CB2b: Choose ways to express oneself through creating content (Express oneself through a writing piece about family members).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -3559,8 +3540,7 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 13 “Appearance”, the teacher shows pictures of characters with different appearances and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Character – Appearance”; pairs ask and answer about the characters in the picture and then come up to fill in their sentences
+          <t>Digital Competence (NLS): 4.2CB2a: Choose simple ways to protect personal data (photos). (e.g., Understanding that photos of one's appearance are personal data and shouldn't be shared with strangers).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -3631,8 +3611,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 13 “Appearance”, the teacher shows pictures on the screen and plays the audio, pausing after each part so pupils tick the person described
-Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song What do your parents look like? with scrolling lyrics on the screen for the whole class to sing
+          <t>Digital Competence (NLS):3.2CB2a: Choose ways to modify and refine descriptive sentences (Students can select appropriate adjectives or phrases to correct or improve a digital description of someone's appearance).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -3703,8 +3682,7 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 13 “Appearance”, the teacher plays the model audio of sentences describing appearance
-Digital competence Domain 5 (Basic, level 2): In the Warm-up message-passing game, after each turn the teacher shows the original sentence describing a person on the screen; the two teams compare what they said with the original sentence
+          <t>Digital Competence (NLS):2.4CB2a: Select simple digital tools for group collaboration (e.g., choose between creating a digital slide or a paper poster to present survey results).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -3775,8 +3753,7 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 14 “Daily activities”, the teacher shows pictures of daily activities with the new words on the screen and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows a shared table “Time – What I do”; pairs ask and answer about each other's daily timetables, then come up to write their sentences
+          <t>Digital Competence (1.3CB2b):Recognize where data is organized (sequence of activities).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -3847,8 +3824,7 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 14 “Daily activities”, the teacher shows pictures of daily activities with the new words on the screen and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the Warm-up game Change chairs, the teacher shows the commands on the screen for the whole class to read together; pupils listen and change seats if the sentence is true for them
+          <t>Digital Competence: - 1.2CB2a: Detect the reliability of time information. (Specifically: Identify illogical or incorrect time information presented in digital formats like slides or online schedules).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -3919,8 +3895,7 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 14 “Daily activities”, the teacher shows pictures of daily activities with the new words on the screen and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows a shared table “Time – What I do”; pairs ask and answer about each other's daily timetables, then come up to write their sentences
+          <t>Competences:  Digital Competence 3.1CB2a: Identify how to create content (Activity Diary).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -3991,9 +3966,7 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 15 “My family's weekends”, the teacher shows pictures of places in the town with their names on the screen and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows a shared table “Weekend places – What people do there”; pairs ask and answer and then come up to fill in their sentences
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -4133,9 +4106,7 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 15 “My family's weekends”, the teacher plays the model audio, first slowly and then at normal speed, and shows the sentences with stress marks…
-Digital competence Domain 5 (Basic, level 2): In the Warm-up game Matching, the teacher shows two shuffled columns of words and pictures; groups try matching them and then click check
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -4445,8 +4416,7 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 16 “Weather”, the teacher plays the model audio of the two sounds learnt, first slowly and then at normal speed, and shows example sentences with…
-Digital competence Domain 5 (Basic, level 2): In the Warm-up game Slap the board, the teacher shows the words learnt on the screen; two teams listen to the teacher and come up to touch the right word
+          <t>Digital Competence 3.2CB2a (Refining and integrating content): Pupils can collect, refine (edit/adjust), and integrate weather data from different sources (text, pictures, personal experience) to create a structured weather report/chart.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -4517,8 +4487,7 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and tick of Unit 17 “In the city”, the teacher shows the pictures on the screen and plays the audio, pausing after each part for pupils to tick the places mentioned
-Digital competence Domain 5 (Basic, level 2): In the Warm-up game Memory game, the teacher shows a set of cards with direction and place words and then hides them one by one; groups remember and name the missing card
+          <t>Digital Competency (2.5CB2a - Choosing simple behavioral standards - Urban Civility): Pupils can identify and choose correct behaviors (civility) when interacting with digital simulations of traffic situations (choosing the "civil" action on a digital platform/game).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -4589,8 +4558,7 @@
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 17 “In the city”, the teacher shows a street map on the screen and plays the model audio of sentences giving directions
-Digital competence Domain 5 (Basic, level 2): In the speaking activity, the teacher shows a neighbourhood map marked with a starting point and a destination; pairs take turns giving directions in English
+          <t>Digital Competency 1.2CB2a (Detecting the reliability of directions): Pupils can evaluate whether the direction heard matches the visual map/cues provided in the book to ensure the information is reliable before choosing the answer.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -4661,9 +4629,7 @@
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and tick of Unit 17 “In the city”, the teacher shows the pictures on the screen and plays the audio, pausing after each part for pupils to tick the places mentioned
-Digital competence Domain 5 (Basic, level 2): In the Warm-up game Memory game, the teacher shows a set of cards with direction and place words and then hides them one by one; groups remember and name the missing card
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -4733,8 +4699,7 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the activity Look, listen and repeat of Unit 18 “At the shopping centre”, the teacher shows a picture of a shopping centre with the names of the shops and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Shop – Things you can buy there”; pairs ask and answer and then come up to fill in their sentences
+          <t>Digital Competency 4.1CB2b (Distinguishing simple risks - shopping safety): Identify potential risks at a shopping centre (e.g., getting lost, keeping personal belongings safe) and understand that knowing the exact location of shops helps minimize these risks.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -4875,8 +4840,7 @@
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the activity Look, listen and repeat of Unit 18 “At the shopping centre”, the teacher shows a picture of a shopping centre with the names of the shops and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Shop – Things you can buy there”; pairs ask and answer and then come up to fill in their sentences
+          <t>Digital Competency (3.1CB2a): Create simple digital content (a discount poster). Students learn how to organize information (items, prices, discounts) into a visual digital format.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -4947,9 +4911,7 @@
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 19, the teacher shows pictures on the screen and plays the audio, pausing after each part so pupils tick the animal mentioned
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Animal – Habitat – Food”; pairs ask and answer and then come up to fill in their sentences
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -5019,9 +4981,7 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 19 “The animal world”, the teacher shows pictures of animals on the screen and plays the model audio of the describing sentences
-Digital competence Domain 5 (Basic, level 2): In the Warm-up animal-guessing game, the teacher shows mostly covered pictures; groups guess the names in English and raise their hands to answer
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -5091,8 +5051,7 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 19, the teacher shows pictures on the screen and plays the audio, pausing after each part so pupils tick the animal mentioned
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Animal – Habitat – Food”; pairs ask and answer and then come up to fill in their sentences
+          <t>Competency 3.1CB2b: Express oneself (drawing/telling about favorite animals). Students use their creativity to draw and their speaking skills to present their personal connection to the animal world.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -5163,8 +5122,7 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 20 “At summer camp”, the teacher shows pictures of summer camp activities with their names and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Summer camp activity – Why I like it”; pairs ask and answer and then come up to fill in their sentences
+          <t>Digital Competency (2.6CB2b): Protecting online reputation (when sharing photos). Students recognize which photos are appropriate to share on social media to maintain a positive digital image for themselves and their friends.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -5305,8 +5263,7 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 20 “At summer camp”, the teacher shows pictures of summer camp activities with their names and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Summer camp activity – Why I like it”; pairs ask and answer and then come up to fill in their sentences
+          <t>Digital Competency 2.4CB2a (Choose digital collaboration tools for group planning): Students can discuss and select appropriate digital platforms (e.g., Padlet, Zalo, PowerPoint) to collect images and plan their group's project presentation.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
